--- a/hw/Terminal_offset.xlsx
+++ b/hw/Terminal_offset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Daten\Daniel\ele\bat_source\hw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B84D832-0AEF-4B1C-A945-629A4F0B6E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE074F38-E60B-4434-B641-9D8BE7414BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17325" xr2:uid="{7FE45C81-C561-428F-9A74-EE5EFF6E3519}"/>
   </bookViews>
@@ -78,12 +78,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -98,8 +104,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1230,21 +1237,21 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>19</v>
-      </c>
-      <c r="B22">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <f t="shared" si="0"/>
         <v>18.894443627691185</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <f t="shared" si="1"/>
         <v>18.899999999999999</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <f t="shared" si="2"/>
         <v>5.5563723088134509E-3</v>
       </c>
@@ -11532,8 +11539,8 @@
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
-        <cfvo type="percentile" val="5"/>
         <cfvo type="percentile" val="10"/>
+        <cfvo type="percentile" val="20"/>
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
